--- a/wooclap/imports/03_Search_Part_1.xlsx
+++ b/wooclap/imports/03_Search_Part_1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$6</definedName>

--- a/wooclap/imports/03_Search_Part_1.xlsx
+++ b/wooclap/imports/03_Search_Part_1.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L01-C01 · One route takes two roads of 3 minutes each. Another takes three roads of 1 minute each. Which route is faster?</t>
+          <t>L01-C01 · Three routes reach the same destination: P has road times 4 + 4, Q has 1 + 2 + 2, and R has 6 + 1 minutes. Which comparison of road count and total time is correct?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -530,22 +530,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The second route: 3 minutes in total.</t>
+          <t>P and R tie for fewest roads; Q is fastest at 5 minutes.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>The first route: fewer roads always means less travel time.</t>
+          <t>P and R tie for fewest roads; R is fastest at 1 minute.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Both routes take 3 minutes.</t>
+          <t>Q uses the fewest roads and is fastest at 5 minutes.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>The first route: 3 minutes in total.</t>
+          <t>P and R tie for fewest roads and must tie for fastest time.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>L01-C02 · A search uses a waiting line: the first item added is the first served. B is waiting before C. Which is served first?</t>
+          <t>L01-C02 · A search removes the oldest waiting path and adds children at the back. Its queue is [B, C, D], next first. B is expanded, adding E then F; C is then expanded, adding H. No node is a goal. Which two nodes are selected next?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>B.</t>
+          <t>D, then E.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>C.</t>
+          <t>E, then F.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>The item with the longest name.</t>
+          <t>H, then D.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Both must be served at once.</t>
+          <t>D, then H.</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>L01-C03 · You put book B on a pile, then put book C on top. If you remove the top book first, which comes out first?</t>
+          <t>L01-C03 · A search removes the most recently added path. It pushes B, then C, then D onto an empty stack. After selecting D, it pushes J, then K. J and K have no children; K is then selected. No node is a goal. Which two nodes are selected next?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>B.</t>
+          <t>C, then B.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Whichever book was cheaper.</t>
+          <t>C, then J.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Both books must come out at once.</t>
+          <t>J, then B.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>C.</t>
+          <t>J, then C.</t>
         </is>
       </c>
       <c r="H4" s="2" t="n"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>L01-C04 · How does iterative deepening search work?</t>
+          <t>L01-C04 · In a finite tree, the only goals are G at depth 3 with path cost 12, and H at depth 4 with path cost 4. All edge costs are positive. Iterative deepening increases its limit from 0 by one each time and stops at its first goal. What does it return, and why?</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -650,22 +650,22 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>It searches only the start state and then stops.</t>
+          <t>H: positive edge costs make the deeper goal cheaper to find.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>It stores every possible path before starting.</t>
+          <t>H: iterative deepening compares total costs across all limits.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>It repeats depth-limited search, gradually allowing greater depth.</t>
+          <t>G: the depth-3 pass reaches it before H is allowed; fewest edges need not mean lowest cost.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>It chooses roads only by their names.</t>
+          <t>G: the first goal found must have minimum cost whenever all edge costs are positive.</t>
         </is>
       </c>
       <c r="H5" s="3" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>L01-C05 · You found a route to the destination that costs 10. Another route has cost 2 so far and needs one final step costing 1. Which is cheaper?</t>
+          <t>L01-C05 · Only these directed edges exist: S→G costs 9, S→A costs 2, A→G costs 8, S→B costs 4, and B→G costs 1. After expanding S, a search selects the waiting path with the lowest cost so far. Which path comes next, and which complete route is cheapest?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -690,22 +690,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>The first route, because it was found first.</t>
+          <t>Next S→G; cheapest S→G, because a goal has already been discovered.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>The second route, with total cost 2.</t>
+          <t>Next S→B; cheapest S→B→G, because its final edge is cheapest.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>The second route, with total cost 3.</t>
+          <t>Next S→A; cheapest S→B→G, with total cost 5.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Both routes cost 10.</t>
+          <t>Next S→A; cheapest S→A→G, because A is selected first.</t>
         </is>
       </c>
       <c r="H6" s="2" t="n"/>
